--- a/19AA/ib_results_19AA_ibbylayer.xlsx
+++ b/19AA/ib_results_19AA_ibbylayer.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\1DSubsidenceModeling-MF6CSUB\multib\1DSubsidenceModeling-MF6CSUB\19AA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lsaberi\Documents\clay_thicknesses\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{050EED17-F581-4367-B709-2D1B193081F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B432243-6D76-4EBC-ABD3-474E3386A05A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,6 +22,9 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
+    <t>Layer</t>
+  </si>
+  <si>
     <t>Aquifer Unit</t>
   </si>
   <si>
@@ -47,9 +50,6 @@
   </si>
   <si>
     <t>Lower</t>
-  </si>
-  <si>
-    <t>Layer</t>
   </si>
 </sst>
 </file>
@@ -68,7 +68,6 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -422,42 +421,36 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="12" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="3">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="4">
-        <v>1</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>6</v>
+      <c r="B2" s="3" t="s">
+        <v>7</v>
       </c>
       <c r="C2" s="2">
         <v>1</v>
@@ -476,8 +469,8 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="4"/>
-      <c r="B3" s="4"/>
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
       <c r="C3" s="2">
         <v>2</v>
       </c>
@@ -495,8 +488,8 @@
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4"/>
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
       <c r="C4" s="2">
         <v>3</v>
       </c>
@@ -514,8 +507,8 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="4"/>
-      <c r="B5" s="4"/>
+      <c r="A5" s="3"/>
+      <c r="B5" s="3"/>
       <c r="C5" s="2">
         <v>4</v>
       </c>
@@ -533,8 +526,8 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="4"/>
-      <c r="B6" s="4"/>
+      <c r="A6" s="3"/>
+      <c r="B6" s="3"/>
       <c r="C6" s="2">
         <v>5</v>
       </c>
@@ -552,8 +545,8 @@
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="4"/>
-      <c r="B7" s="4"/>
+      <c r="A7" s="3"/>
+      <c r="B7" s="3"/>
       <c r="C7" s="2">
         <v>6</v>
       </c>
@@ -571,8 +564,8 @@
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="4"/>
-      <c r="B8" s="4"/>
+      <c r="A8" s="3"/>
+      <c r="B8" s="3"/>
       <c r="C8" s="2">
         <v>7</v>
       </c>
@@ -590,11 +583,11 @@
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="3">
+      <c r="A9" s="4">
         <v>2</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>7</v>
+      <c r="B9" s="4" t="s">
+        <v>8</v>
       </c>
       <c r="C9" s="2">
         <v>8</v>
@@ -613,11 +606,11 @@
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="4">
+      <c r="A10" s="3">
         <v>3</v>
       </c>
-      <c r="B10" s="4" t="s">
-        <v>8</v>
+      <c r="B10" s="3" t="s">
+        <v>9</v>
       </c>
       <c r="C10" s="2">
         <v>9</v>
@@ -636,8 +629,8 @@
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="4"/>
-      <c r="B11" s="4"/>
+      <c r="A11" s="3"/>
+      <c r="B11" s="3"/>
       <c r="C11" s="2">
         <v>10</v>
       </c>
@@ -655,8 +648,8 @@
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="4"/>
-      <c r="B12" s="4"/>
+      <c r="A12" s="3"/>
+      <c r="B12" s="3"/>
       <c r="C12" s="2">
         <v>11</v>
       </c>
@@ -674,8 +667,8 @@
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="4"/>
-      <c r="B13" s="4"/>
+      <c r="A13" s="3"/>
+      <c r="B13" s="3"/>
       <c r="C13" s="2">
         <v>12</v>
       </c>
@@ -693,8 +686,8 @@
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="4"/>
-      <c r="B14" s="4"/>
+      <c r="A14" s="3"/>
+      <c r="B14" s="3"/>
       <c r="C14" s="2">
         <v>13</v>
       </c>
@@ -712,8 +705,8 @@
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="4"/>
-      <c r="B15" s="4"/>
+      <c r="A15" s="3"/>
+      <c r="B15" s="3"/>
       <c r="C15" s="2">
         <v>14</v>
       </c>
